--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486758</v>
+        <v>121488693</v>
       </c>
       <c r="B2" t="n">
         <v>78604</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499597</v>
+        <v>499553</v>
       </c>
       <c r="R2" t="n">
-        <v>6820748</v>
+        <v>6820781</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486761</v>
+        <v>121486762</v>
       </c>
       <c r="B3" t="n">
         <v>78604</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499508</v>
+        <v>499499</v>
       </c>
       <c r="R3" t="n">
-        <v>6820812</v>
+        <v>6820796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486760</v>
+        <v>121486761</v>
       </c>
       <c r="B4" t="n">
         <v>78604</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499572</v>
+        <v>499508</v>
       </c>
       <c r="R4" t="n">
-        <v>6820871</v>
+        <v>6820812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486762</v>
+        <v>121486758</v>
       </c>
       <c r="B5" t="n">
         <v>78604</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499499</v>
+        <v>499597</v>
       </c>
       <c r="R5" t="n">
-        <v>6820796</v>
+        <v>6820748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121488693</v>
+        <v>121486759</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499553</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>6820781</v>
+        <v>6820762</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486759</v>
+        <v>121486760</v>
       </c>
       <c r="B7" t="n">
         <v>78604</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499572</v>
       </c>
       <c r="R7" t="n">
-        <v>6820762</v>
+        <v>6820871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121488693</v>
+        <v>121486760</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499553</v>
+        <v>499572</v>
       </c>
       <c r="R2" t="n">
-        <v>6820781</v>
+        <v>6820871</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>121486762</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486761</v>
+        <v>121486759</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499508</v>
+        <v>499602</v>
       </c>
       <c r="R4" t="n">
-        <v>6820812</v>
+        <v>6820762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486758</v>
+        <v>121486761</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499597</v>
+        <v>499508</v>
       </c>
       <c r="R5" t="n">
-        <v>6820748</v>
+        <v>6820812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486759</v>
+        <v>121486758</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499602</v>
+        <v>499597</v>
       </c>
       <c r="R6" t="n">
-        <v>6820762</v>
+        <v>6820748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486760</v>
+        <v>121488693</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499572</v>
+        <v>499553</v>
       </c>
       <c r="R7" t="n">
-        <v>6820871</v>
+        <v>6820781</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486759</v>
+        <v>121486761</v>
       </c>
       <c r="B4" t="n">
         <v>78607</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499602</v>
+        <v>499508</v>
       </c>
       <c r="R4" t="n">
-        <v>6820762</v>
+        <v>6820812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486761</v>
+        <v>121488693</v>
       </c>
       <c r="B5" t="n">
         <v>78607</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499508</v>
+        <v>499553</v>
       </c>
       <c r="R5" t="n">
-        <v>6820812</v>
+        <v>6820781</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121488693</v>
+        <v>121486759</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499553</v>
+        <v>499602</v>
       </c>
       <c r="R7" t="n">
-        <v>6820781</v>
+        <v>6820762</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486760</v>
+        <v>121486761</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499572</v>
+        <v>499508</v>
       </c>
       <c r="R2" t="n">
-        <v>6820871</v>
+        <v>6820812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>121486762</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486761</v>
+        <v>121486760</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499508</v>
+        <v>499572</v>
       </c>
       <c r="R4" t="n">
-        <v>6820812</v>
+        <v>6820871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121488693</v>
+        <v>121486759</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499553</v>
+        <v>499602</v>
       </c>
       <c r="R5" t="n">
-        <v>6820781</v>
+        <v>6820762</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>121486758</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486759</v>
+        <v>121488693</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499553</v>
       </c>
       <c r="R7" t="n">
-        <v>6820762</v>
+        <v>6820781</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486761</v>
+        <v>121486758</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499508</v>
+        <v>499597</v>
       </c>
       <c r="R2" t="n">
-        <v>6820812</v>
+        <v>6820748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486762</v>
+        <v>121488693</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499499</v>
+        <v>499553</v>
       </c>
       <c r="R3" t="n">
-        <v>6820796</v>
+        <v>6820781</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>121486760</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486759</v>
+        <v>121486762</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499602</v>
+        <v>499499</v>
       </c>
       <c r="R5" t="n">
-        <v>6820762</v>
+        <v>6820796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486758</v>
+        <v>121486761</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499597</v>
+        <v>499508</v>
       </c>
       <c r="R6" t="n">
-        <v>6820748</v>
+        <v>6820812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121488693</v>
+        <v>121486759</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499553</v>
+        <v>499602</v>
       </c>
       <c r="R7" t="n">
-        <v>6820781</v>
+        <v>6820762</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121488693</v>
+        <v>121486762</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499553</v>
+        <v>499499</v>
       </c>
       <c r="R3" t="n">
-        <v>6820781</v>
+        <v>6820796</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486760</v>
+        <v>121488693</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499572</v>
+        <v>499553</v>
       </c>
       <c r="R4" t="n">
-        <v>6820871</v>
+        <v>6820781</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486762</v>
+        <v>121486761</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499499</v>
+        <v>499508</v>
       </c>
       <c r="R5" t="n">
-        <v>6820796</v>
+        <v>6820812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486761</v>
+        <v>121486759</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499508</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>6820812</v>
+        <v>6820762</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486759</v>
+        <v>121486760</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499572</v>
       </c>
       <c r="R7" t="n">
-        <v>6820762</v>
+        <v>6820871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486758</v>
+        <v>121486760</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499597</v>
+        <v>499572</v>
       </c>
       <c r="R2" t="n">
-        <v>6820748</v>
+        <v>6820871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486762</v>
+        <v>121486759</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499499</v>
+        <v>499602</v>
       </c>
       <c r="R3" t="n">
-        <v>6820796</v>
+        <v>6820762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121488693</v>
+        <v>121486761</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499553</v>
+        <v>499508</v>
       </c>
       <c r="R4" t="n">
-        <v>6820781</v>
+        <v>6820812</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486761</v>
+        <v>121486758</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499508</v>
+        <v>499597</v>
       </c>
       <c r="R5" t="n">
-        <v>6820812</v>
+        <v>6820748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486759</v>
+        <v>121488693</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499602</v>
+        <v>499553</v>
       </c>
       <c r="R6" t="n">
-        <v>6820762</v>
+        <v>6820781</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486760</v>
+        <v>121486762</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499572</v>
+        <v>499499</v>
       </c>
       <c r="R7" t="n">
-        <v>6820871</v>
+        <v>6820796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486760</v>
+        <v>121486761</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499572</v>
+        <v>499508</v>
       </c>
       <c r="R2" t="n">
-        <v>6820871</v>
+        <v>6820812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486759</v>
+        <v>121486762</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499602</v>
+        <v>499499</v>
       </c>
       <c r="R3" t="n">
-        <v>6820762</v>
+        <v>6820796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486761</v>
+        <v>121486759</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499508</v>
+        <v>499602</v>
       </c>
       <c r="R4" t="n">
-        <v>6820812</v>
+        <v>6820762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486758</v>
+        <v>121488693</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499597</v>
+        <v>499553</v>
       </c>
       <c r="R5" t="n">
-        <v>6820748</v>
+        <v>6820781</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121488693</v>
+        <v>121486760</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499553</v>
+        <v>499572</v>
       </c>
       <c r="R6" t="n">
-        <v>6820781</v>
+        <v>6820871</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486762</v>
+        <v>121486758</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499499</v>
+        <v>499597</v>
       </c>
       <c r="R7" t="n">
-        <v>6820796</v>
+        <v>6820748</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486761</v>
+        <v>121486762</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499508</v>
+        <v>499499</v>
       </c>
       <c r="R2" t="n">
-        <v>6820812</v>
+        <v>6820796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486762</v>
+        <v>121488693</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499499</v>
+        <v>499553</v>
       </c>
       <c r="R3" t="n">
-        <v>6820796</v>
+        <v>6820781</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486759</v>
+        <v>121486760</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499602</v>
+        <v>499572</v>
       </c>
       <c r="R4" t="n">
-        <v>6820762</v>
+        <v>6820871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121488693</v>
+        <v>121486759</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499553</v>
+        <v>499602</v>
       </c>
       <c r="R5" t="n">
-        <v>6820781</v>
+        <v>6820762</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson, Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486760</v>
+        <v>121486761</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499572</v>
+        <v>499508</v>
       </c>
       <c r="R6" t="n">
-        <v>6820871</v>
+        <v>6820812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>121486758</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486761</v>
+        <v>121486758</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499508</v>
+        <v>499597</v>
       </c>
       <c r="R6" t="n">
-        <v>6820812</v>
+        <v>6820748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486758</v>
+        <v>121486761</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499597</v>
+        <v>499508</v>
       </c>
       <c r="R7" t="n">
-        <v>6820748</v>
+        <v>6820812</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486760</v>
+        <v>121488693</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499572</v>
+        <v>499553</v>
       </c>
       <c r="R2" t="n">
-        <v>6820871</v>
+        <v>6820781</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486759</v>
+        <v>121486762</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499602</v>
+        <v>499499</v>
       </c>
       <c r="R3" t="n">
-        <v>6820762</v>
+        <v>6820796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486762</v>
+        <v>121486761</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499499</v>
+        <v>499508</v>
       </c>
       <c r="R4" t="n">
-        <v>6820796</v>
+        <v>6820812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486758</v>
+        <v>121486759</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499597</v>
+        <v>499602</v>
       </c>
       <c r="R5" t="n">
-        <v>6820748</v>
+        <v>6820762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121488693</v>
+        <v>121486760</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499553</v>
+        <v>499572</v>
       </c>
       <c r="R6" t="n">
-        <v>6820781</v>
+        <v>6820871</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486761</v>
+        <v>121486758</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499508</v>
+        <v>499597</v>
       </c>
       <c r="R7" t="n">
-        <v>6820812</v>
+        <v>6820748</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23560-2023 artfynd.xlsx
+++ b/artfynd/A 23560-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121488693</v>
+        <v>121486758</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälsingland, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499553</v>
+        <v>499597</v>
       </c>
       <c r="R2" t="n">
-        <v>6820781</v>
+        <v>6820748</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486762</v>
+        <v>121488693</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Hälsingland, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499499</v>
+        <v>499553</v>
       </c>
       <c r="R3" t="n">
-        <v>6820796</v>
+        <v>6820781</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486760</v>
+        <v>121486762</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499572</v>
+        <v>499499</v>
       </c>
       <c r="R6" t="n">
-        <v>6820871</v>
+        <v>6820796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486758</v>
+        <v>121486760</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499597</v>
+        <v>499572</v>
       </c>
       <c r="R7" t="n">
-        <v>6820748</v>
+        <v>6820871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
